--- a/PS-VRP/Dati_input/Estrazione 8/Commesse_da_tagliare.xlsx
+++ b/PS-VRP/Dati_input/Estrazione 8/Commesse_da_tagliare.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frenc\Documents\GitHub\progettoIS\PS-VRP\Dati_input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frenc\Documents\GitHub\progettoIS\PS-VRP\Dati_input\Estrazione 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08FF4CA-6D57-454E-903C-0043BF47DFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FEC4D1-D4B0-4928-A745-FE88AEC6BB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10020" yWindow="3240" windowWidth="16665" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -986,34 +986,40 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>245089</v>
+        <v>252814</v>
       </c>
       <c r="B2" s="3">
-        <v>45844</v>
+        <v>45846</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3">
-        <v>46022</v>
+        <v>45852</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>122665</v>
+        <v>6010</v>
       </c>
       <c r="G2" s="2">
-        <v>2679</v>
+        <v>300</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J2" s="2">
-        <v>395</v>
+        <v>205</v>
       </c>
       <c r="K2" s="2">
-        <v>1185</v>
+        <v>615</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>64</v>
@@ -1034,7 +1040,7 @@
         <v>43</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>45</v>
@@ -1049,7 +1055,7 @@
         <v>48</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>50</v>
@@ -1073,51 +1079,51 @@
         <v>56</v>
       </c>
       <c r="AF2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="2">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>252713</v>
+        <v>252230</v>
       </c>
       <c r="B3" s="3">
-        <v>45844</v>
+        <v>45840</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="3">
-        <v>45856</v>
+        <v>45821</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>108932</v>
+        <v>7575</v>
       </c>
       <c r="G3" s="2">
-        <v>3000</v>
+        <v>450</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J3" s="2">
-        <v>209</v>
+        <v>400</v>
       </c>
       <c r="K3" s="2">
-        <v>836</v>
+        <v>800</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>39</v>
@@ -1126,25 +1132,25 @@
         <v>40</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="W3" s="4" t="s">
         <v>48</v>
@@ -1156,7 +1162,7 @@
         <v>50</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="AA3" s="4" t="s">
         <v>52</v>
@@ -1174,15 +1180,15 @@
         <v>56</v>
       </c>
       <c r="AF3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" s="2">
-        <v>244</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>251632</v>
+        <v>252087</v>
       </c>
       <c r="B4" s="3">
         <v>45845</v>
@@ -1191,31 +1197,31 @@
         <v>75</v>
       </c>
       <c r="D4" s="3">
-        <v>45845</v>
+        <v>45837</v>
       </c>
       <c r="E4" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>70621</v>
+        <v>4260</v>
       </c>
       <c r="G4" s="2">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J4" s="2">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="K4" s="2">
-        <v>780</v>
+        <v>720</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>67</v>
@@ -1233,7 +1239,7 @@
         <v>42</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>44</v>
@@ -1242,10 +1248,10 @@
         <v>45</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>48</v>
@@ -1254,10 +1260,10 @@
         <v>49</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="AA4" s="4" t="s">
         <v>52</v>
@@ -1275,48 +1281,45 @@
         <v>56</v>
       </c>
       <c r="AF4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>403</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>252334</v>
+        <v>252085</v>
       </c>
       <c r="B5" s="3">
-        <v>45849</v>
+        <v>45846</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D5" s="3">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>58391</v>
+        <v>3426</v>
       </c>
       <c r="G5" s="2">
-        <v>4192</v>
+        <v>200</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J5" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K5" s="2">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>67</v>
@@ -1376,51 +1379,48 @@
         <v>56</v>
       </c>
       <c r="AF5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="2">
-        <v>352</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>252157</v>
+        <v>243335</v>
       </c>
       <c r="B6" s="3">
-        <v>45848</v>
+        <v>45502</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3">
-        <v>45826</v>
+        <v>45506</v>
       </c>
       <c r="E6" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>47619</v>
+        <v>33004</v>
       </c>
       <c r="G6" s="2">
-        <v>1000</v>
+        <v>3746</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="2">
-        <v>86</v>
+        <v>410</v>
       </c>
       <c r="K6" s="2">
-        <v>688</v>
+        <v>1230</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>39</v>
@@ -1429,7 +1429,7 @@
         <v>40</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>42</v>
@@ -1438,7 +1438,7 @@
         <v>43</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>45</v>
@@ -1453,7 +1453,7 @@
         <v>48</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>50</v>
@@ -1477,15 +1477,15 @@
         <v>56</v>
       </c>
       <c r="AF6" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="2">
-        <v>344</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>252686</v>
+        <v>252723</v>
       </c>
       <c r="B7" s="3">
         <v>45845</v>
@@ -1494,34 +1494,34 @@
         <v>35</v>
       </c>
       <c r="D7" s="3">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>39498</v>
+        <v>18475</v>
       </c>
       <c r="G7" s="2">
-        <v>3030</v>
+        <v>1399</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="K7" s="2">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>39</v>
@@ -1554,7 +1554,7 @@
         <v>48</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>50</v>
@@ -1581,42 +1581,42 @@
         <v>1</v>
       </c>
       <c r="AG7" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>252999</v>
+        <v>250284</v>
       </c>
       <c r="B8" s="3">
-        <v>45844</v>
+        <v>45733</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="3">
-        <v>45875</v>
+        <v>45728</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>39101</v>
+        <v>17562</v>
       </c>
       <c r="G8" s="2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J8" s="2">
-        <v>765</v>
+        <v>102</v>
       </c>
       <c r="K8" s="2">
-        <v>765</v>
+        <v>714</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>67</v>
@@ -1652,7 +1652,7 @@
         <v>48</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>50</v>
@@ -1677,47 +1677,47 @@
       </c>
       <c r="AF8" s="2">
         <v>0</v>
-      </c>
-      <c r="AG8" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>251231</v>
+        <v>252244</v>
       </c>
       <c r="B9" s="3">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
-        <v>45841</v>
+        <v>45845</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>37477</v>
+        <v>12909</v>
       </c>
       <c r="G9" s="2">
-        <v>2637</v>
+        <v>614</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="2">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="K9" s="2">
-        <v>1075</v>
+        <v>855</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>39</v>
@@ -1726,7 +1726,7 @@
         <v>40</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>42</v>
@@ -1735,7 +1735,7 @@
         <v>43</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T9" s="4" t="s">
         <v>45</v>
@@ -1750,7 +1750,7 @@
         <v>48</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>50</v>
@@ -1774,39 +1774,33 @@
         <v>56</v>
       </c>
       <c r="AF9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="2">
-        <v>160</v>
-      </c>
-      <c r="AH9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI9" s="2">
-        <v>40034</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>243335</v>
+        <v>252243</v>
       </c>
       <c r="B10" s="3">
-        <v>45502</v>
+        <v>45845</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="3">
-        <v>45506</v>
+        <v>45852</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>33004</v>
+        <v>11605</v>
       </c>
       <c r="G10" s="2">
-        <v>3746</v>
+        <v>552</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>57</v>
@@ -1815,16 +1809,16 @@
         <v>37</v>
       </c>
       <c r="J10" s="2">
-        <v>410</v>
+        <v>285</v>
       </c>
       <c r="K10" s="2">
-        <v>1230</v>
+        <v>855</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>39</v>
@@ -1842,7 +1836,7 @@
         <v>43</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="T10" s="4" t="s">
         <v>45</v>
@@ -1857,7 +1851,7 @@
         <v>48</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>50</v>
@@ -1881,51 +1875,51 @@
         <v>56</v>
       </c>
       <c r="AF10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="2">
-        <v>105</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>251790</v>
+        <v>252549</v>
       </c>
       <c r="B11" s="3">
-        <v>45845</v>
+        <v>45847</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D11" s="3">
-        <v>45838</v>
+        <v>45858</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>28207</v>
+        <v>11111</v>
       </c>
       <c r="G11" s="2">
-        <v>2029</v>
+        <v>500</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="2">
-        <v>480</v>
+        <v>290</v>
       </c>
       <c r="K11" s="2">
-        <v>960</v>
+        <v>580</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>39</v>
@@ -1934,7 +1928,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>42</v>
@@ -1943,7 +1937,7 @@
         <v>43</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T11" s="4" t="s">
         <v>45</v>
@@ -1982,45 +1976,48 @@
         <v>56</v>
       </c>
       <c r="AF11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>245623</v>
+        <v>252547</v>
       </c>
       <c r="B12" s="3">
-        <v>45844</v>
+        <v>45847</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D12" s="3">
-        <v>45682</v>
+        <v>45842</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>26419</v>
+        <v>9740</v>
       </c>
       <c r="G12" s="2">
-        <v>1536</v>
+        <v>660</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J12" s="2">
-        <v>840</v>
+        <v>216</v>
       </c>
       <c r="K12" s="2">
-        <v>840</v>
+        <v>864</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>39</v>
@@ -2029,7 +2026,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q12" s="4" t="s">
         <v>42</v>
@@ -2038,7 +2035,7 @@
         <v>43</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T12" s="4" t="s">
         <v>45</v>
@@ -2053,7 +2050,7 @@
         <v>48</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="Y12" s="4" t="s">
         <v>50</v>
@@ -2080,15 +2077,15 @@
         <v>0</v>
       </c>
       <c r="AG12" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>252652</v>
+        <v>252467</v>
       </c>
       <c r="B13" s="3">
-        <v>45845</v>
+        <v>45848</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>75</v>
@@ -2100,22 +2097,25 @@
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <v>22321</v>
+        <v>9740</v>
       </c>
       <c r="G13" s="2">
-        <v>1000</v>
+        <v>660</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J13" s="2">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="K13" s="2">
-        <v>560</v>
+        <v>800</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>67</v>
@@ -2176,47 +2176,44 @@
       </c>
       <c r="AF13" s="2">
         <v>0</v>
-      </c>
-      <c r="AG13" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>252899</v>
+        <v>252220</v>
       </c>
       <c r="B14" s="3">
-        <v>45849</v>
+        <v>45846</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="3">
-        <v>45862</v>
+        <v>45824</v>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>21668</v>
+        <v>9662</v>
       </c>
       <c r="G14" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J14" s="2">
-        <v>345</v>
+        <v>225</v>
       </c>
       <c r="K14" s="2">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>67</v>
@@ -2279,104 +2276,56 @@
         <v>0</v>
       </c>
       <c r="AG14" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>252466</v>
+        <v>251310</v>
       </c>
       <c r="B15" s="3">
-        <v>45844</v>
+        <v>45770</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="3">
-        <v>45848</v>
+        <v>45769</v>
       </c>
       <c r="E15" s="2">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8611</v>
+      </c>
+      <c r="G15" s="2">
+        <v>336</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="2">
+        <v>410</v>
+      </c>
+      <c r="K15" s="2">
+        <v>820</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF15" s="2">
         <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>18947</v>
-      </c>
-      <c r="G15" s="2">
-        <v>500</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="2">
-        <v>800</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="T15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U15" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="V15" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="W15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X15" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y15" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z15" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF15" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>252723</v>
+        <v>252546</v>
       </c>
       <c r="B16" s="3">
         <v>45845</v>
@@ -2385,16 +2334,16 @@
         <v>35</v>
       </c>
       <c r="D16" s="3">
-        <v>45869</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>18475</v>
+        <v>6556</v>
       </c>
       <c r="G16" s="2">
-        <v>1399</v>
+        <v>548</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>57</v>
@@ -2403,13 +2352,13 @@
         <v>37</v>
       </c>
       <c r="J16" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K16" s="2">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>64</v>
@@ -2472,48 +2421,48 @@
         <v>1</v>
       </c>
       <c r="AG16" s="2">
-        <v>86</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>251674</v>
+        <v>252207</v>
       </c>
       <c r="B17" s="3">
-        <v>45842</v>
+        <v>45845</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
-        <v>45845</v>
+        <v>45834</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
-        <v>17655</v>
+        <v>6186</v>
       </c>
       <c r="G17" s="2">
-        <v>1000</v>
+        <v>479</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="2">
-        <v>60</v>
+        <v>415</v>
       </c>
       <c r="K17" s="2">
-        <v>780</v>
+        <v>830</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>39</v>
@@ -2522,25 +2471,25 @@
         <v>40</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T17" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="W17" s="4" t="s">
         <v>48</v>
@@ -2549,10 +2498,10 @@
         <v>49</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="AA17" s="4" t="s">
         <v>52</v>
@@ -2570,250 +2519,263 @@
         <v>56</v>
       </c>
       <c r="AF17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="2">
-        <v>104</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>250284</v>
-      </c>
-      <c r="B18" s="3">
-        <v>45733</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="3">
-        <v>45728</v>
-      </c>
-      <c r="E18" s="2">
-        <v>6</v>
-      </c>
-      <c r="F18" s="2">
-        <v>17562</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="A18" s="12">
+        <v>252286</v>
+      </c>
+      <c r="B18" s="13">
+        <v>45845</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="13">
+        <v>45840</v>
+      </c>
+      <c r="E18" s="12">
+        <v>3</v>
+      </c>
+      <c r="F18" s="12">
+        <v>6152</v>
+      </c>
+      <c r="G18" s="12">
+        <v>300</v>
+      </c>
+      <c r="H18" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="2">
-        <v>102</v>
-      </c>
-      <c r="K18" s="2">
-        <v>714</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N18" s="4" t="s">
+      <c r="J18" s="12">
+        <v>190</v>
+      </c>
+      <c r="K18" s="12">
+        <v>570</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="P18" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="S18" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="T18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="U18" s="4" t="s">
+      <c r="U18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="V18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="W18" s="4" t="s">
+      <c r="W18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="Y18" s="4" t="s">
+      <c r="Y18" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Z18" s="4" t="s">
+      <c r="Z18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AA18" s="4" t="s">
+      <c r="AA18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="AB18" s="4" t="s">
+      <c r="AB18" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="AC18" s="4" t="s">
+      <c r="AC18" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="AD18" s="4" t="s">
+      <c r="AD18" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AE18" s="4" t="s">
+      <c r="AE18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AF18" s="2">
+      <c r="AF18" s="12">
         <v>0</v>
+      </c>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI18" s="12">
+        <v>40032</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>252277</v>
-      </c>
-      <c r="B19" s="3">
-        <v>45847</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="12">
+        <v>252284</v>
+      </c>
+      <c r="B19" s="13">
+        <v>45846</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="3">
-        <v>45828</v>
-      </c>
-      <c r="E19" s="2">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2">
-        <v>17391</v>
-      </c>
-      <c r="G19" s="2">
-        <v>900</v>
-      </c>
-      <c r="I19" s="4" t="s">
+      <c r="D19" s="13">
+        <v>45840</v>
+      </c>
+      <c r="E19" s="12">
+        <v>3</v>
+      </c>
+      <c r="F19" s="12">
+        <v>6152</v>
+      </c>
+      <c r="G19" s="12">
+        <v>300</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="2">
-        <v>340</v>
-      </c>
-      <c r="K19" s="2">
-        <v>680</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="J19" s="12">
+        <v>190</v>
+      </c>
+      <c r="K19" s="12">
+        <v>570</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P19" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="S19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="T19" s="4" t="s">
+      <c r="T19" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="U19" s="4" t="s">
+      <c r="U19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="V19" s="4" t="s">
+      <c r="V19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="W19" s="4" t="s">
+      <c r="W19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="X19" s="4" t="s">
+      <c r="X19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="Y19" s="4" t="s">
+      <c r="Y19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Z19" s="4" t="s">
+      <c r="Z19" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AA19" s="4" t="s">
+      <c r="AA19" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="AB19" s="4" t="s">
+      <c r="AB19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="AC19" s="4" t="s">
+      <c r="AC19" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="AD19" s="4" t="s">
+      <c r="AD19" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AE19" s="4" t="s">
+      <c r="AE19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AF19" s="2">
+      <c r="AF19" s="12">
         <v>0</v>
       </c>
-      <c r="AG19" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" s="4" t="s">
+      <c r="AG19" s="12">
+        <v>33</v>
+      </c>
+      <c r="AH19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="AI19" s="2">
-        <v>40024</v>
+      <c r="AI19" s="12">
+        <v>40032</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>252456</v>
+        <v>252371</v>
       </c>
       <c r="B20" s="3">
-        <v>45847</v>
+        <v>45845</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D20" s="3">
-        <v>45848</v>
+        <v>45838</v>
       </c>
       <c r="E20" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2">
-        <v>17335</v>
+        <v>6005</v>
       </c>
       <c r="G20" s="2">
-        <v>800</v>
+        <v>462</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J20" s="2">
-        <v>174</v>
+        <v>385</v>
       </c>
       <c r="K20" s="2">
-        <v>696</v>
+        <v>1155</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N20" s="4" t="s">
         <v>39</v>
@@ -2822,7 +2784,7 @@
         <v>40</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>42</v>
@@ -2831,7 +2793,7 @@
         <v>43</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="T20" s="4" t="s">
         <v>45</v>
@@ -2846,7 +2808,7 @@
         <v>48</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>50</v>
@@ -2870,51 +2832,51 @@
         <v>56</v>
       </c>
       <c r="AF20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="2">
-        <v>72</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>251919</v>
+        <v>252285</v>
       </c>
       <c r="B21" s="3">
         <v>45845</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D21" s="3">
-        <v>45824</v>
+        <v>45840</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>16806</v>
+        <v>5537</v>
       </c>
       <c r="G21" s="2">
-        <v>1581</v>
+        <v>300</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J21" s="2">
-        <v>430</v>
+        <v>225</v>
       </c>
       <c r="K21" s="2">
-        <v>860</v>
+        <v>675</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N21" s="4" t="s">
         <v>39</v>
@@ -2923,7 +2885,7 @@
         <v>40</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q21" s="4" t="s">
         <v>42</v>
@@ -2932,7 +2894,7 @@
         <v>43</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T21" s="4" t="s">
         <v>45</v>
@@ -2947,7 +2909,7 @@
         <v>48</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="Y21" s="4" t="s">
         <v>50</v>
@@ -2971,42 +2933,57 @@
         <v>56</v>
       </c>
       <c r="AF21" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="2">
+        <v>24</v>
+      </c>
+      <c r="AH21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>40032</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>252140</v>
+        <v>252997</v>
       </c>
       <c r="B22" s="3">
         <v>45845</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D22" s="3">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <v>15689</v>
+        <v>4802</v>
       </c>
       <c r="G22" s="2">
-        <v>1236</v>
+        <v>557</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J22" s="2">
-        <v>286</v>
+        <v>408</v>
       </c>
       <c r="K22" s="2">
-        <v>858</v>
+        <v>1224</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="N22" s="4" t="s">
         <v>39</v>
@@ -3015,7 +2992,7 @@
         <v>40</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>42</v>
@@ -3024,7 +3001,7 @@
         <v>43</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="T22" s="4" t="s">
         <v>45</v>
@@ -3039,7 +3016,7 @@
         <v>48</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Y22" s="4" t="s">
         <v>50</v>
@@ -3063,54 +3040,51 @@
         <v>56</v>
       </c>
       <c r="AF22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI22" s="2">
-        <v>40037</v>
+        <v>1</v>
+      </c>
+      <c r="AG22" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>243525</v>
-      </c>
-      <c r="B23" s="6">
-        <v>45845</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="6">
-        <v>45842</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>15598</v>
+      <c r="A23" s="2">
+        <v>252899</v>
+      </c>
+      <c r="B23" s="3">
+        <v>45849</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3">
+        <v>45862</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>21668</v>
       </c>
       <c r="G23" s="2">
-        <v>1122</v>
+        <v>1000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J23" s="2">
-        <v>480</v>
+        <v>345</v>
       </c>
       <c r="K23" s="2">
-        <v>960</v>
+        <v>690</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>39</v>
@@ -3119,7 +3093,7 @@
         <v>40</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>42</v>
@@ -3128,7 +3102,7 @@
         <v>43</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T23" s="4" t="s">
         <v>45</v>
@@ -3167,45 +3141,48 @@
         <v>56</v>
       </c>
       <c r="AF23" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="2">
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>243529</v>
-      </c>
-      <c r="B24" s="6">
+      <c r="A24" s="2">
+        <v>252978</v>
+      </c>
+      <c r="B24" s="3">
         <v>45845</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="6">
-        <v>45842</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5">
-        <v>15598</v>
+      <c r="D24" s="3">
+        <v>45824</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2796</v>
       </c>
       <c r="G24" s="2">
-        <v>1122</v>
+        <v>245</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J24" s="2">
-        <v>480</v>
+        <v>580</v>
       </c>
       <c r="K24" s="2">
-        <v>960</v>
+        <v>1160</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>64</v>
@@ -3226,7 +3203,7 @@
         <v>43</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="T24" s="4" t="s">
         <v>45</v>
@@ -3241,7 +3218,7 @@
         <v>48</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="Y24" s="4" t="s">
         <v>50</v>
@@ -3266,47 +3243,50 @@
       </c>
       <c r="AF24" s="2">
         <v>1</v>
+      </c>
+      <c r="AG24" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>251798</v>
+        <v>252334</v>
       </c>
       <c r="B25" s="3">
-        <v>45843</v>
+        <v>45849</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="3">
-        <v>45853</v>
+        <v>45842</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>14795</v>
+        <v>58391</v>
       </c>
       <c r="G25" s="2">
-        <v>784</v>
+        <v>4192</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J25" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K25" s="2">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N25" s="4" t="s">
         <v>39</v>
@@ -3315,7 +3295,7 @@
         <v>40</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q25" s="4" t="s">
         <v>42</v>
@@ -3324,7 +3304,7 @@
         <v>43</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T25" s="4" t="s">
         <v>45</v>
@@ -3366,30 +3346,30 @@
         <v>0</v>
       </c>
       <c r="AG25" s="2">
-        <v>117</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>252336</v>
+        <v>252456</v>
       </c>
       <c r="B26" s="3">
-        <v>45848</v>
+        <v>45847</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D26" s="3">
-        <v>45842</v>
+        <v>45848</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2">
-        <v>14433</v>
+        <v>17335</v>
       </c>
       <c r="G26" s="2">
-        <v>1048</v>
+        <v>800</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>116</v>
@@ -3398,13 +3378,13 @@
         <v>37</v>
       </c>
       <c r="J26" s="2">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="K26" s="2">
-        <v>800</v>
+        <v>696</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>67</v>
@@ -3467,12 +3447,12 @@
         <v>0</v>
       </c>
       <c r="AG26" s="2">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>252755</v>
+        <v>252336</v>
       </c>
       <c r="B27" s="3">
         <v>45848</v>
@@ -3481,31 +3461,31 @@
         <v>75</v>
       </c>
       <c r="D27" s="3">
-        <v>45855</v>
+        <v>45842</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
       </c>
       <c r="F27" s="2">
-        <v>13149</v>
+        <v>14433</v>
       </c>
       <c r="G27" s="2">
-        <v>500</v>
+        <v>1048</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J27" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K27" s="2">
-        <v>570</v>
+        <v>800</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>67</v>
@@ -3568,48 +3548,48 @@
         <v>0</v>
       </c>
       <c r="AG27" s="2">
-        <v>54</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>252244</v>
+        <v>251926</v>
       </c>
       <c r="B28" s="3">
-        <v>45845</v>
+        <v>45848</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D28" s="3">
-        <v>45845</v>
+        <v>45847</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>12909</v>
+        <v>9470</v>
       </c>
       <c r="G28" s="2">
-        <v>614</v>
+        <v>500</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J28" s="2">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="K28" s="2">
-        <v>855</v>
+        <v>660</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>39</v>
@@ -3618,7 +3598,7 @@
         <v>40</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>42</v>
@@ -3627,7 +3607,7 @@
         <v>43</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T28" s="4" t="s">
         <v>45</v>
@@ -3666,80 +3646,80 @@
         <v>56</v>
       </c>
       <c r="AF28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>251685</v>
-      </c>
-      <c r="B29" s="3">
-        <v>45846</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="A29" s="8">
+        <v>251495</v>
+      </c>
+      <c r="B29" s="9">
+        <v>45848</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="3">
-        <v>45853</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>11851</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1100</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" s="4" t="s">
+      <c r="D29" s="9">
+        <v>45847</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8">
+        <v>8681</v>
+      </c>
+      <c r="G29" s="8">
+        <v>500</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J29" s="2">
-        <v>200</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M29" s="4" t="s">
+      <c r="J29" s="8">
+        <v>175</v>
+      </c>
+      <c r="K29" s="8">
+        <v>700</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="O29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="P29" s="4" t="s">
+      <c r="P29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="Q29" s="4" t="s">
+      <c r="Q29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="R29" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S29" s="4" t="s">
+      <c r="S29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="T29" s="4" t="s">
+      <c r="T29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="U29" s="4" t="s">
+      <c r="U29" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="V29" s="4" t="s">
+      <c r="V29" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="W29" s="10" t="s">
         <v>48</v>
       </c>
       <c r="X29" s="4" t="s">
@@ -3770,48 +3750,48 @@
         <v>0</v>
       </c>
       <c r="AG29" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>252243</v>
+        <v>252790</v>
       </c>
       <c r="B30" s="3">
-        <v>45845</v>
+        <v>45848</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3">
-        <v>45852</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
-        <v>11605</v>
+        <v>1453</v>
       </c>
       <c r="G30" s="2">
-        <v>552</v>
+        <v>106</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J30" s="2">
-        <v>285</v>
+        <v>200</v>
       </c>
       <c r="K30" s="2">
-        <v>855</v>
+        <v>800</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N30" s="4" t="s">
         <v>39</v>
@@ -3820,7 +3800,7 @@
         <v>40</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q30" s="4" t="s">
         <v>42</v>
@@ -3829,7 +3809,7 @@
         <v>43</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T30" s="4" t="s">
         <v>45</v>
@@ -3868,45 +3848,48 @@
         <v>56</v>
       </c>
       <c r="AF30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" s="2">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>252364</v>
+        <v>252157</v>
       </c>
       <c r="B31" s="3">
-        <v>45846</v>
+        <v>45848</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D31" s="3">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
-        <v>11346</v>
+        <v>47619</v>
       </c>
       <c r="G31" s="2">
-        <v>500</v>
+        <v>1000</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J31" s="2">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="K31" s="2">
-        <v>546</v>
+        <v>688</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>67</v>
@@ -3966,51 +3949,45 @@
         <v>56</v>
       </c>
       <c r="AF31" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG31" s="2">
-        <v>48</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>252549</v>
+        <v>252466</v>
       </c>
       <c r="B32" s="3">
-        <v>45847</v>
+        <v>45844</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D32" s="3">
-        <v>45858</v>
+        <v>45848</v>
       </c>
       <c r="E32" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2">
-        <v>11111</v>
+        <v>18947</v>
       </c>
       <c r="G32" s="2">
         <v>500</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J32" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="K32" s="2">
-        <v>580</v>
+        <v>800</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="N32" s="4" t="s">
         <v>39</v>
@@ -4019,37 +3996,37 @@
         <v>40</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="T32" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="V32" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="W32" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="Z32" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="AA32" s="4" t="s">
         <v>52</v>
@@ -4173,43 +4150,43 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>252237</v>
+        <v>252350</v>
       </c>
       <c r="B34" s="3">
-        <v>45842</v>
+        <v>45847</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3">
-        <v>45839</v>
+        <v>45846</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>10194</v>
+        <v>6226</v>
       </c>
       <c r="G34" s="2">
-        <v>623</v>
+        <v>320</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J34" s="2">
-        <v>360</v>
+        <v>650</v>
       </c>
       <c r="K34" s="2">
-        <v>1080</v>
+        <v>650</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="N34" s="4" t="s">
         <v>39</v>
@@ -4218,22 +4195,22 @@
         <v>40</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q34" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T34" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="V34" s="4" t="s">
         <v>47</v>
@@ -4242,7 +4219,7 @@
         <v>48</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="Y34" s="4" t="s">
         <v>50</v>
@@ -4266,48 +4243,48 @@
         <v>56</v>
       </c>
       <c r="AF34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" s="2">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>252547</v>
-      </c>
-      <c r="B35" s="3">
-        <v>45847</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="A35" s="5">
+        <v>252345</v>
+      </c>
+      <c r="B35" s="6">
         <v>45842</v>
       </c>
-      <c r="E35" s="2">
+      <c r="C35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="6">
+        <v>45846</v>
+      </c>
+      <c r="E35" s="5">
         <v>0</v>
       </c>
-      <c r="F35" s="2">
-        <v>9740</v>
+      <c r="F35" s="5">
+        <v>5199</v>
       </c>
       <c r="G35" s="2">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J35" s="2">
-        <v>216</v>
+        <v>405</v>
       </c>
       <c r="K35" s="2">
-        <v>864</v>
+        <v>810</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>67</v>
@@ -4370,48 +4347,48 @@
         <v>0</v>
       </c>
       <c r="AG35" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>252467</v>
+        <v>252201</v>
       </c>
       <c r="B36" s="3">
-        <v>45848</v>
+        <v>45845</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D36" s="3">
-        <v>45855</v>
+        <v>45828</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
-        <v>9740</v>
+        <v>4093</v>
       </c>
       <c r="G36" s="2">
-        <v>660</v>
+        <v>154</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J36" s="2">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="K36" s="2">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>39</v>
@@ -4420,7 +4397,7 @@
         <v>40</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="4" t="s">
         <v>42</v>
@@ -4429,7 +4406,7 @@
         <v>43</v>
       </c>
       <c r="S36" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T36" s="4" t="s">
         <v>45</v>
@@ -4468,48 +4445,48 @@
         <v>56</v>
       </c>
       <c r="AF36" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AG36" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>252220</v>
+        <v>243569</v>
       </c>
       <c r="B37" s="3">
-        <v>45846</v>
+        <v>45561</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D37" s="3">
-        <v>45824</v>
+        <v>45551</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
-        <v>9662</v>
+        <v>2601</v>
       </c>
       <c r="G37" s="2">
-        <v>500</v>
+        <v>364</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J37" s="2">
-        <v>225</v>
+        <v>570</v>
       </c>
       <c r="K37" s="2">
-        <v>675</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>89</v>
+        <v>1140</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>39</v>
@@ -4518,7 +4495,7 @@
         <v>40</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q37" s="4" t="s">
         <v>42</v>
@@ -4527,7 +4504,7 @@
         <v>43</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="T37" s="4" t="s">
         <v>45</v>
@@ -4542,7 +4519,7 @@
         <v>48</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="Y37" s="4" t="s">
         <v>50</v>
@@ -4566,51 +4543,48 @@
         <v>56</v>
       </c>
       <c r="AF37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>252063</v>
+        <v>252999</v>
       </c>
       <c r="B38" s="3">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D38" s="3">
-        <v>45839</v>
+        <v>45875</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" s="2">
-        <v>9593</v>
+        <v>39101</v>
       </c>
       <c r="G38" s="2">
-        <v>609</v>
+        <v>2000</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J38" s="2">
-        <v>420</v>
+        <v>765</v>
       </c>
       <c r="K38" s="2">
-        <v>840</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>73</v>
+        <v>765</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>39</v>
@@ -4619,7 +4593,7 @@
         <v>40</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q38" s="4" t="s">
         <v>42</v>
@@ -4628,7 +4602,7 @@
         <v>43</v>
       </c>
       <c r="S38" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T38" s="4" t="s">
         <v>45</v>
@@ -4643,7 +4617,7 @@
         <v>48</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>50</v>
@@ -4667,48 +4641,51 @@
         <v>56</v>
       </c>
       <c r="AF38" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG38" s="2">
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>251926</v>
+        <v>252237</v>
       </c>
       <c r="B39" s="3">
-        <v>45848</v>
+        <v>45842</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D39" s="3">
-        <v>45847</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>9470</v>
+        <v>10194</v>
       </c>
       <c r="G39" s="2">
-        <v>500</v>
+        <v>623</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J39" s="2">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="K39" s="2">
-        <v>660</v>
+        <v>1080</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>102</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="N39" s="4" t="s">
         <v>39</v>
@@ -4717,22 +4694,22 @@
         <v>40</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q39" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T39" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="V39" s="4" t="s">
         <v>47</v>
@@ -4741,7 +4718,7 @@
         <v>48</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="Y39" s="4" t="s">
         <v>50</v>
@@ -4765,42 +4742,51 @@
         <v>56</v>
       </c>
       <c r="AF39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>252418</v>
+        <v>252638</v>
       </c>
       <c r="B40" s="3">
-        <v>45841</v>
+        <v>45847</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D40" s="3">
-        <v>45838</v>
+        <v>45844</v>
       </c>
       <c r="E40" s="2">
         <v>6</v>
       </c>
       <c r="F40" s="2">
-        <v>8985</v>
+        <v>7379</v>
       </c>
       <c r="G40" s="2">
-        <v>285</v>
+        <v>500</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>77</v>
+        <v>37</v>
+      </c>
+      <c r="J40" s="2">
+        <v>215</v>
       </c>
       <c r="K40" s="2">
-        <v>600</v>
+        <v>860</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>38</v>
+        <v>115</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="N40" s="4" t="s">
         <v>39</v>
@@ -4809,37 +4795,37 @@
         <v>40</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="Q40" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="T40" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="W40" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="Y40" s="4" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Z40" s="4" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="AA40" s="4" t="s">
         <v>52</v>
@@ -4857,75 +4843,80 @@
         <v>56</v>
       </c>
       <c r="AF40" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AG40" s="2">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
-        <v>252476</v>
-      </c>
-      <c r="B41" s="9">
+      <c r="A41" s="2">
+        <v>252785</v>
+      </c>
+      <c r="B41" s="3">
         <v>45846</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="9">
-        <v>45845</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3</v>
-      </c>
-      <c r="F41" s="8">
-        <v>8681</v>
-      </c>
-      <c r="G41" s="8">
-        <v>500</v>
-      </c>
-      <c r="H41" s="11"/>
-      <c r="I41" s="10" t="s">
+      <c r="D41" s="3">
+        <v>45862</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>6690</v>
+      </c>
+      <c r="G41" s="2">
+        <v>340</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J41" s="8">
-        <v>345</v>
-      </c>
-      <c r="K41" s="8">
-        <v>690</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M41" s="10" t="s">
+      <c r="J41" s="2">
+        <v>85</v>
+      </c>
+      <c r="K41" s="2">
+        <v>425</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N41" s="10" t="s">
+      <c r="N41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O41" s="10" t="s">
+      <c r="O41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P41" s="10" t="s">
+      <c r="P41" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Q41" s="10" t="s">
+      <c r="Q41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R41" s="10" t="s">
+      <c r="R41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="S41" s="10" t="s">
+      <c r="S41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="T41" s="10" t="s">
+      <c r="T41" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="U41" s="10" t="s">
+      <c r="U41" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="V41" s="10" t="s">
+      <c r="V41" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="W41" s="10" t="s">
+      <c r="W41" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X41" s="4" t="s">
@@ -4953,84 +4944,84 @@
         <v>56</v>
       </c>
       <c r="AF41" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="2">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
-        <v>251495</v>
-      </c>
-      <c r="B42" s="9">
-        <v>45848</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" s="9">
-        <v>45847</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3</v>
-      </c>
-      <c r="F42" s="8">
-        <v>8681</v>
-      </c>
-      <c r="G42" s="8">
-        <v>500</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="I42" s="10" t="s">
+      <c r="A42" s="2">
+        <v>244828</v>
+      </c>
+      <c r="B42" s="3">
+        <v>45845</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="3">
+        <v>45845</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>5203</v>
+      </c>
+      <c r="G42" s="2">
+        <v>318</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J42" s="8">
-        <v>175</v>
-      </c>
-      <c r="K42" s="8">
-        <v>700</v>
-      </c>
-      <c r="L42" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N42" s="10" t="s">
+      <c r="J42" s="2">
+        <v>360</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1080</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O42" s="10" t="s">
+      <c r="O42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P42" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q42" s="10" t="s">
+      <c r="P42" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R42" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S42" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="T42" s="10" t="s">
+      <c r="R42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="S42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T42" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="U42" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V42" s="10" t="s">
+      <c r="U42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="V42" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="W42" s="10" t="s">
+      <c r="W42" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="Y42" s="4" t="s">
         <v>50</v>
@@ -5054,89 +5045,149 @@
         <v>56</v>
       </c>
       <c r="AF42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" s="2">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>251310</v>
+        <v>252784</v>
       </c>
       <c r="B43" s="3">
-        <v>45770</v>
+        <v>45846</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D43" s="3">
-        <v>45769</v>
+        <v>45862</v>
       </c>
       <c r="E43" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2">
-        <v>8611</v>
+        <v>3237</v>
       </c>
       <c r="G43" s="2">
-        <v>336</v>
+        <v>165</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J43" s="2">
-        <v>410</v>
+        <v>85</v>
       </c>
       <c r="K43" s="2">
-        <v>820</v>
+        <v>425</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>73</v>
+        <v>89</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>74</v>
+        <v>39</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X43" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y43" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z43" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD43" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE43" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="AF43" s="2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AG43" s="2">
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>252047</v>
+        <v>252402</v>
       </c>
       <c r="B44" s="3">
-        <v>45841</v>
+        <v>45840</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="3">
-        <v>45837</v>
+        <v>45835</v>
       </c>
       <c r="E44" s="2">
         <v>6</v>
       </c>
       <c r="F44" s="2">
-        <v>8506</v>
+        <v>3009</v>
       </c>
       <c r="G44" s="2">
-        <v>601</v>
+        <v>174</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J44" s="2">
-        <v>470</v>
+        <v>255</v>
       </c>
       <c r="K44" s="2">
-        <v>940</v>
+        <v>1020</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>64</v>
@@ -5197,48 +5248,42 @@
       </c>
       <c r="AF44" s="2">
         <v>1</v>
+      </c>
+      <c r="AG44" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>252298</v>
+        <v>252980</v>
       </c>
       <c r="B45" s="3">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D45" s="3">
-        <v>45831</v>
+        <v>45908</v>
       </c>
       <c r="E45" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F45" s="2">
-        <v>8492</v>
+        <v>2049</v>
       </c>
       <c r="G45" s="2">
-        <v>460</v>
+        <v>100</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="K45" s="2">
         <v>700</v>
       </c>
-      <c r="L45" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="N45" s="4" t="s">
         <v>39</v>
       </c>
@@ -5246,37 +5291,37 @@
         <v>40</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="Q45" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="T45" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="W45" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X45" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="AA45" s="4" t="s">
         <v>52</v>
@@ -5294,146 +5339,92 @@
         <v>56</v>
       </c>
       <c r="AF45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>252146</v>
+        <v>252983</v>
       </c>
       <c r="B46" s="3">
-        <v>45841</v>
+        <v>45847</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D46" s="3">
-        <v>45837</v>
+        <v>45862</v>
       </c>
       <c r="E46" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F46" s="2">
-        <v>7996</v>
+        <v>1912</v>
       </c>
       <c r="G46" s="2">
-        <v>565</v>
+        <v>97</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J46" s="2">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="K46" s="2">
-        <v>940</v>
+        <v>425</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R46" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="V46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X46" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y46" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z46" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA46" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB46" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC46" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD46" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE46" s="4" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="AF46" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>243524</v>
+        <v>252783</v>
       </c>
       <c r="B47" s="3">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D47" s="3">
-        <v>45842</v>
+        <v>45862</v>
       </c>
       <c r="E47" s="2">
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <v>7994</v>
+        <v>1434</v>
       </c>
       <c r="G47" s="2">
-        <v>575</v>
+        <v>73</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J47" s="2">
-        <v>480</v>
+        <v>85</v>
       </c>
       <c r="K47" s="2">
-        <v>960</v>
+        <v>425</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>39</v>
@@ -5442,7 +5433,7 @@
         <v>40</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q47" s="4" t="s">
         <v>42</v>
@@ -5451,7 +5442,7 @@
         <v>43</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T47" s="4" t="s">
         <v>45</v>
@@ -5490,51 +5481,51 @@
         <v>56</v>
       </c>
       <c r="AF47" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG47" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>252230</v>
+        <v>252636</v>
       </c>
       <c r="B48" s="3">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D48" s="3">
-        <v>45821</v>
+        <v>45848</v>
       </c>
       <c r="E48" s="2">
         <v>6</v>
       </c>
       <c r="F48" s="2">
-        <v>7575</v>
+        <v>1353</v>
       </c>
       <c r="G48" s="2">
-        <v>450</v>
+        <v>71</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J48" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="K48" s="2">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>39</v>
@@ -5543,7 +5534,7 @@
         <v>40</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>42</v>
@@ -5552,7 +5543,7 @@
         <v>43</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T48" s="4" t="s">
         <v>45</v>
@@ -5591,45 +5582,48 @@
         <v>56</v>
       </c>
       <c r="AF48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>252470</v>
+        <v>252713</v>
       </c>
       <c r="B49" s="3">
-        <v>45849</v>
+        <v>45844</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D49" s="3">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="E49" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2">
-        <v>7500</v>
+        <v>108932</v>
       </c>
       <c r="G49" s="2">
-        <v>300</v>
+        <v>3000</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J49" s="2">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="K49" s="2">
-        <v>480</v>
+        <v>836</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>67</v>
@@ -5641,13 +5635,13 @@
         <v>40</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="Q49" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="S49" s="4" t="s">
         <v>44</v>
@@ -5656,10 +5650,10 @@
         <v>45</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="W49" s="4" t="s">
         <v>48</v>
@@ -5671,7 +5665,7 @@
         <v>50</v>
       </c>
       <c r="Z49" s="4" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="AA49" s="4" t="s">
         <v>52</v>
@@ -5689,48 +5683,48 @@
         <v>56</v>
       </c>
       <c r="AF49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG49" s="2">
-        <v>36</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>252638</v>
+        <v>251632</v>
       </c>
       <c r="B50" s="3">
-        <v>45847</v>
+        <v>45845</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D50" s="3">
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="E50" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F50" s="2">
-        <v>7379</v>
+        <v>70621</v>
       </c>
       <c r="G50" s="2">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J50" s="2">
-        <v>215</v>
+        <v>60</v>
       </c>
       <c r="K50" s="2">
-        <v>860</v>
+        <v>780</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>67</v>
@@ -5748,7 +5742,7 @@
         <v>42</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S50" s="4" t="s">
         <v>44</v>
@@ -5757,10 +5751,10 @@
         <v>45</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="W50" s="4" t="s">
         <v>48</v>
@@ -5769,10 +5763,10 @@
         <v>49</v>
       </c>
       <c r="Y50" s="4" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="Z50" s="4" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="AA50" s="4" t="s">
         <v>52</v>
@@ -5793,45 +5787,45 @@
         <v>0</v>
       </c>
       <c r="AG50" s="2">
-        <v>32</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>252785</v>
+        <v>251674</v>
       </c>
       <c r="B51" s="3">
-        <v>45846</v>
+        <v>45842</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="3">
-        <v>45862</v>
+        <v>45845</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="2">
-        <v>6690</v>
+        <v>17655</v>
       </c>
       <c r="G51" s="2">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J51" s="2">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="K51" s="2">
-        <v>425</v>
+        <v>780</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>67</v>
@@ -5849,7 +5843,7 @@
         <v>42</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S51" s="4" t="s">
         <v>44</v>
@@ -5858,10 +5852,10 @@
         <v>45</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="W51" s="4" t="s">
         <v>48</v>
@@ -5870,10 +5864,10 @@
         <v>49</v>
       </c>
       <c r="Y51" s="4" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="Z51" s="4" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="AA51" s="4" t="s">
         <v>52</v>
@@ -5891,15 +5885,15 @@
         <v>56</v>
       </c>
       <c r="AF51" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG51" s="2">
-        <v>180</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>252546</v>
+        <v>251919</v>
       </c>
       <c r="B52" s="3">
         <v>45845</v>
@@ -5908,34 +5902,34 @@
         <v>35</v>
       </c>
       <c r="D52" s="3">
-        <v>45839</v>
+        <v>45824</v>
       </c>
       <c r="E52" s="2">
         <v>0</v>
       </c>
       <c r="F52" s="2">
-        <v>6556</v>
+        <v>16806</v>
       </c>
       <c r="G52" s="2">
-        <v>548</v>
+        <v>1581</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J52" s="2">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K52" s="2">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>39</v>
@@ -5968,7 +5962,7 @@
         <v>48</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="Y52" s="4" t="s">
         <v>50</v>
@@ -5994,43 +5988,43 @@
       <c r="AF52" s="2">
         <v>1</v>
       </c>
-      <c r="AG52" s="2">
-        <v>24</v>
-      </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>252144</v>
+        <v>251798</v>
       </c>
       <c r="B53" s="3">
-        <v>45841</v>
+        <v>45843</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3">
-        <v>45837</v>
+        <v>45853</v>
       </c>
       <c r="E53" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2">
-        <v>6496</v>
+        <v>14795</v>
       </c>
       <c r="G53" s="2">
-        <v>459</v>
+        <v>784</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J53" s="2">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="K53" s="2">
-        <v>940</v>
+        <v>750</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>64</v>
@@ -6090,45 +6084,48 @@
         <v>56</v>
       </c>
       <c r="AF53" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG53" s="2">
+        <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>252350</v>
+        <v>252755</v>
       </c>
       <c r="B54" s="3">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D54" s="3">
-        <v>45846</v>
+        <v>45855</v>
       </c>
       <c r="E54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="2">
-        <v>6226</v>
+        <v>13149</v>
       </c>
       <c r="G54" s="2">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J54" s="2">
-        <v>650</v>
+        <v>190</v>
       </c>
       <c r="K54" s="2">
-        <v>650</v>
+        <v>570</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>67</v>
@@ -6164,7 +6161,7 @@
         <v>48</v>
       </c>
       <c r="X54" s="4" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="Y54" s="4" t="s">
         <v>50</v>
@@ -6191,12 +6188,12 @@
         <v>0</v>
       </c>
       <c r="AG54" s="2">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>252207</v>
+        <v>252298</v>
       </c>
       <c r="B55" s="3">
         <v>45845</v>
@@ -6205,31 +6202,31 @@
         <v>35</v>
       </c>
       <c r="D55" s="3">
-        <v>45834</v>
+        <v>45831</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F55" s="2">
-        <v>6186</v>
+        <v>8492</v>
       </c>
       <c r="G55" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J55" s="2">
-        <v>415</v>
+        <v>140</v>
       </c>
       <c r="K55" s="2">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>64</v>
@@ -6292,257 +6289,247 @@
         <v>1</v>
       </c>
       <c r="AG55" s="2">
-        <v>28</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
-        <v>252286</v>
-      </c>
-      <c r="B56" s="13">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>252071</v>
+      </c>
+      <c r="B56" s="3">
+        <v>45838</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="3">
+        <v>45820</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>5488</v>
+      </c>
+      <c r="G56" s="2">
+        <v>251</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" s="2">
+        <v>251</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1004</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S56" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V56" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W56" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X56" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y56" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z56" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA56" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC56" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE56" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>252686</v>
+      </c>
+      <c r="B57" s="3">
         <v>45845</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" s="13">
-        <v>45840</v>
-      </c>
-      <c r="E56" s="12">
-        <v>3</v>
-      </c>
-      <c r="F56" s="12">
-        <v>6152</v>
-      </c>
-      <c r="G56" s="12">
-        <v>300</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I56" s="14" t="s">
+      <c r="C57" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="3">
+        <v>45859</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
+        <v>39498</v>
+      </c>
+      <c r="G57" s="2">
+        <v>3030</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J56" s="12">
-        <v>190</v>
-      </c>
-      <c r="K56" s="12">
-        <v>570</v>
-      </c>
-      <c r="L56" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="M56" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="N56" s="14" t="s">
+      <c r="J57" s="2">
+        <v>420</v>
+      </c>
+      <c r="K57" s="2">
+        <v>840</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N57" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O56" s="14" t="s">
+      <c r="O57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P56" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q56" s="14" t="s">
+      <c r="P57" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q57" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R56" s="14" t="s">
+      <c r="R57" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="S56" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="T56" s="14" t="s">
+      <c r="S57" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="U56" s="14" t="s">
+      <c r="U57" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="V56" s="14" t="s">
+      <c r="V57" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="W56" s="14" t="s">
+      <c r="W57" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="X56" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y56" s="14" t="s">
+      <c r="X57" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y57" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Z56" s="14" t="s">
+      <c r="Z57" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AA56" s="14" t="s">
+      <c r="AA57" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AB56" s="14" t="s">
+      <c r="AB57" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AC56" s="14" t="s">
+      <c r="AC57" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AD56" s="14" t="s">
+      <c r="AD57" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AE56" s="14" t="s">
+      <c r="AE57" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AF56" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="16"/>
-      <c r="AH56" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI56" s="12">
-        <v>40032</v>
+      <c r="AF57" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="2">
+        <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
-        <v>252284</v>
-      </c>
-      <c r="B57" s="13">
-        <v>45846</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" s="13">
-        <v>45840</v>
-      </c>
-      <c r="E57" s="12">
-        <v>3</v>
-      </c>
-      <c r="F57" s="12">
-        <v>6152</v>
-      </c>
-      <c r="G57" s="12">
-        <v>300</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J57" s="12">
-        <v>190</v>
-      </c>
-      <c r="K57" s="12">
-        <v>570</v>
-      </c>
-      <c r="L57" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="M57" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="N57" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="O57" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="P57" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q57" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="R57" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="S57" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="U57" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="V57" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="W57" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="X57" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y57" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z57" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA57" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB57" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC57" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD57" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE57" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF57" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12">
-        <v>33</v>
-      </c>
-      <c r="AH57" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI57" s="12">
-        <v>40032</v>
-      </c>
-    </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>252814</v>
+        <v>252063</v>
       </c>
       <c r="B58" s="3">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D58" s="3">
-        <v>45852</v>
+        <v>45839</v>
       </c>
       <c r="E58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2">
-        <v>6010</v>
+        <v>9593</v>
       </c>
       <c r="G58" s="2">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J58" s="2">
-        <v>205</v>
+        <v>420</v>
       </c>
       <c r="K58" s="2">
-        <v>615</v>
+        <v>840</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>64</v>
@@ -6602,15 +6589,12 @@
         <v>56</v>
       </c>
       <c r="AF58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>252371</v>
+        <v>251790</v>
       </c>
       <c r="B59" s="3">
         <v>45845</v>
@@ -6625,25 +6609,25 @@
         <v>0</v>
       </c>
       <c r="F59" s="2">
-        <v>6005</v>
+        <v>28207</v>
       </c>
       <c r="G59" s="2">
-        <v>462</v>
+        <v>2029</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J59" s="2">
-        <v>385</v>
+        <v>480</v>
       </c>
       <c r="K59" s="2">
-        <v>1155</v>
+        <v>960</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>64</v>
@@ -6664,7 +6648,7 @@
         <v>43</v>
       </c>
       <c r="S59" s="4" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="T59" s="4" t="s">
         <v>45</v>
@@ -6679,7 +6663,7 @@
         <v>48</v>
       </c>
       <c r="X59" s="4" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="Y59" s="4" t="s">
         <v>50</v>
@@ -6705,46 +6689,46 @@
       <c r="AF59" s="2">
         <v>1</v>
       </c>
-      <c r="AG59" s="2">
-        <v>18</v>
-      </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>252665</v>
-      </c>
-      <c r="B60" s="3">
-        <v>45844</v>
-      </c>
-      <c r="C60" s="4" t="s">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>243525</v>
+      </c>
+      <c r="B60" s="6">
+        <v>45845</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D60" s="3">
-        <v>45902</v>
-      </c>
-      <c r="E60" s="2">
-        <v>6</v>
-      </c>
-      <c r="F60" s="2">
-        <v>5865</v>
+      <c r="D60" s="6">
+        <v>45842</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5">
+        <v>15598</v>
       </c>
       <c r="G60" s="2">
-        <v>300</v>
+        <v>1122</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J60" s="2">
-        <v>775</v>
+        <v>480</v>
       </c>
       <c r="K60" s="2">
-        <v>775</v>
+        <v>960</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>39</v>
@@ -6753,7 +6737,7 @@
         <v>40</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q60" s="4" t="s">
         <v>42</v>
@@ -6762,7 +6746,7 @@
         <v>43</v>
       </c>
       <c r="S60" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T60" s="4" t="s">
         <v>45</v>
@@ -6777,7 +6761,7 @@
         <v>48</v>
       </c>
       <c r="X60" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>50</v>
@@ -6801,51 +6785,48 @@
         <v>56</v>
       </c>
       <c r="AF60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>243529</v>
+      </c>
+      <c r="B61" s="6">
+        <v>45845</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="6">
+        <v>45842</v>
+      </c>
+      <c r="E61" s="5">
         <v>0</v>
       </c>
-      <c r="AG60" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>252285</v>
-      </c>
-      <c r="B61" s="3">
-        <v>45845</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" s="3">
-        <v>45840</v>
-      </c>
-      <c r="E61" s="2">
-        <v>3</v>
-      </c>
-      <c r="F61" s="2">
-        <v>5537</v>
+      <c r="F61" s="5">
+        <v>15598</v>
       </c>
       <c r="G61" s="2">
-        <v>300</v>
+        <v>1122</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J61" s="2">
-        <v>225</v>
+        <v>480</v>
       </c>
       <c r="K61" s="2">
-        <v>675</v>
+        <v>960</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>39</v>
@@ -6854,7 +6835,7 @@
         <v>40</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q61" s="4" t="s">
         <v>42</v>
@@ -6863,7 +6844,7 @@
         <v>43</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T61" s="4" t="s">
         <v>45</v>
@@ -6902,57 +6883,48 @@
         <v>56</v>
       </c>
       <c r="AF61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>251685</v>
+      </c>
+      <c r="B62" s="3">
+        <v>45846</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="3">
+        <v>45853</v>
+      </c>
+      <c r="E62" s="2">
         <v>0</v>
       </c>
-      <c r="AG61" s="2">
-        <v>24</v>
-      </c>
-      <c r="AH61" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI61" s="2">
-        <v>40032</v>
-      </c>
-    </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>252071</v>
-      </c>
-      <c r="B62" s="3">
-        <v>45838</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D62" s="3">
-        <v>45820</v>
-      </c>
-      <c r="E62" s="2">
-        <v>1</v>
-      </c>
       <c r="F62" s="2">
-        <v>5488</v>
+        <v>11851</v>
       </c>
       <c r="G62" s="2">
-        <v>251</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J62" s="2">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="K62" s="2">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N62" s="4" t="s">
         <v>39</v>
@@ -6961,7 +6933,7 @@
         <v>40</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q62" s="4" t="s">
         <v>42</v>
@@ -6970,7 +6942,7 @@
         <v>43</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T62" s="4" t="s">
         <v>45</v>
@@ -7009,15 +6981,15 @@
         <v>56</v>
       </c>
       <c r="AF62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG62" s="2">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>244828</v>
+        <v>243524</v>
       </c>
       <c r="B63" s="3">
         <v>45845</v>
@@ -7026,34 +6998,34 @@
         <v>35</v>
       </c>
       <c r="D63" s="3">
-        <v>45845</v>
+        <v>45842</v>
       </c>
       <c r="E63" s="2">
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>5203</v>
+        <v>7994</v>
       </c>
       <c r="G63" s="2">
-        <v>318</v>
+        <v>575</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J63" s="2">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="K63" s="2">
-        <v>1080</v>
+        <v>960</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="N63" s="4" t="s">
         <v>39</v>
@@ -7068,7 +7040,7 @@
         <v>42</v>
       </c>
       <c r="R63" s="4" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>69</v>
@@ -7077,7 +7049,7 @@
         <v>45</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="V63" s="4" t="s">
         <v>47</v>
@@ -7086,7 +7058,7 @@
         <v>48</v>
       </c>
       <c r="X63" s="4" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="Y63" s="4" t="s">
         <v>50</v>
@@ -7113,10 +7085,10 @@
         <v>1</v>
       </c>
       <c r="AG63" s="2">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>241783</v>
       </c>
@@ -7215,44 +7187,44 @@
       </c>
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>252345</v>
-      </c>
-      <c r="B65" s="6">
+      <c r="A65" s="2">
+        <v>252152</v>
+      </c>
+      <c r="B65" s="3">
         <v>45842</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D65" s="6">
-        <v>45846</v>
-      </c>
-      <c r="E65" s="5">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5">
-        <v>5199</v>
+      <c r="D65" s="3">
+        <v>45828</v>
+      </c>
+      <c r="E65" s="2">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2">
+        <v>3284</v>
       </c>
       <c r="G65" s="2">
-        <v>330</v>
+        <v>216</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J65" s="2">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="K65" s="2">
-        <v>810</v>
+        <v>1005</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N65" s="4" t="s">
         <v>39</v>
@@ -7261,7 +7233,7 @@
         <v>40</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="4" t="s">
         <v>42</v>
@@ -7270,7 +7242,7 @@
         <v>43</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T65" s="4" t="s">
         <v>45</v>
@@ -7309,51 +7281,51 @@
         <v>56</v>
       </c>
       <c r="AF65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG65" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>252997</v>
+        <v>244023</v>
       </c>
       <c r="B66" s="3">
-        <v>45845</v>
+        <v>45552</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D66" s="3">
-        <v>45853</v>
+        <v>45565</v>
       </c>
       <c r="E66" s="2">
         <v>0</v>
       </c>
       <c r="F66" s="2">
-        <v>4802</v>
+        <v>997</v>
       </c>
       <c r="G66" s="2">
-        <v>557</v>
+        <v>59</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J66" s="2">
-        <v>408</v>
+        <v>172</v>
       </c>
       <c r="K66" s="2">
-        <v>1224</v>
+        <v>860</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>38</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>39</v>
@@ -7362,7 +7334,7 @@
         <v>40</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q66" s="4" t="s">
         <v>42</v>
@@ -7371,7 +7343,7 @@
         <v>43</v>
       </c>
       <c r="S66" s="4" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="T66" s="4" t="s">
         <v>45</v>
@@ -7386,7 +7358,7 @@
         <v>48</v>
       </c>
       <c r="X66" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="Y66" s="4" t="s">
         <v>50</v>
@@ -7410,42 +7382,45 @@
         <v>56</v>
       </c>
       <c r="AF66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG66" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>252417</v>
+        <v>245089</v>
       </c>
       <c r="B67" s="3">
-        <v>45840</v>
+        <v>45844</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D67" s="3">
-        <v>45838</v>
+        <v>46022</v>
       </c>
       <c r="E67" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F67" s="2">
-        <v>4711</v>
+        <v>122665</v>
       </c>
       <c r="G67" s="2">
-        <v>222</v>
+        <v>2679</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>77</v>
+        <v>37</v>
+      </c>
+      <c r="J67" s="2">
+        <v>395</v>
       </c>
       <c r="K67" s="2">
-        <v>720</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>89</v>
+        <v>1185</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="N67" s="4" t="s">
         <v>39</v>
@@ -7454,37 +7429,37 @@
         <v>40</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="Q67" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R67" s="4" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="S67" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="T67" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U67" s="4" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="V67" s="4" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="W67" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X67" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="Y67" s="4" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="AA67" s="4" t="s">
         <v>52</v>
@@ -7502,45 +7477,47 @@
         <v>56</v>
       </c>
       <c r="AF67" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AG67" s="2">
+        <v>138</v>
+      </c>
+      <c r="AH67" s="10"/>
+      <c r="AI67" s="11"/>
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>252087</v>
+        <v>251231</v>
       </c>
       <c r="B68" s="3">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D68" s="3">
-        <v>45837</v>
+        <v>45841</v>
       </c>
       <c r="E68" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F68" s="2">
-        <v>4260</v>
+        <v>37477</v>
       </c>
       <c r="G68" s="2">
-        <v>200</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>125</v>
+        <v>2637</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J68" s="2">
-        <v>360</v>
+        <v>215</v>
       </c>
       <c r="K68" s="2">
-        <v>720</v>
+        <v>1075</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>67</v>
@@ -7576,7 +7553,7 @@
         <v>48</v>
       </c>
       <c r="X68" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="Y68" s="4" t="s">
         <v>50</v>
@@ -7600,48 +7577,54 @@
         <v>56</v>
       </c>
       <c r="AF68" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG68" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH68" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI68" s="2">
+        <v>40034</v>
       </c>
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>252201</v>
+        <v>245623</v>
       </c>
       <c r="B69" s="3">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D69" s="3">
-        <v>45828</v>
+        <v>45682</v>
       </c>
       <c r="E69" s="2">
         <v>1</v>
       </c>
       <c r="F69" s="2">
-        <v>4093</v>
+        <v>26419</v>
       </c>
       <c r="G69" s="2">
-        <v>154</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>63</v>
+        <v>1536</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J69" s="2">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="K69" s="2">
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>39</v>
@@ -7674,7 +7657,7 @@
         <v>48</v>
       </c>
       <c r="X69" s="4" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="Y69" s="4" t="s">
         <v>50</v>
@@ -7698,45 +7681,47 @@
         <v>56</v>
       </c>
       <c r="AF69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG69" s="2">
-        <v>12</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="AH69" s="10"/>
+      <c r="AI69" s="11"/>
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>251849</v>
+        <v>252652</v>
       </c>
       <c r="B70" s="3">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D70" s="3">
-        <v>45833</v>
+        <v>45855</v>
       </c>
       <c r="E70" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2">
-        <v>4006</v>
+        <v>22321</v>
       </c>
       <c r="G70" s="2">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J70" s="2">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="K70" s="2">
-        <v>768</v>
+        <v>560</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>67</v>
@@ -7798,49 +7783,45 @@
       <c r="AF70" s="2">
         <v>0</v>
       </c>
-      <c r="AH70" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI70" s="2">
-        <v>40042</v>
-      </c>
+      <c r="AG70" s="2">
+        <v>68</v>
+      </c>
+      <c r="AH70" s="10"/>
+      <c r="AI70" s="11"/>
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>252085</v>
+        <v>252277</v>
       </c>
       <c r="B71" s="3">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D71" s="3">
-        <v>45826</v>
+        <v>45828</v>
       </c>
       <c r="E71" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F71" s="2">
-        <v>3426</v>
+        <v>17391</v>
       </c>
       <c r="G71" s="2">
-        <v>200</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>125</v>
+        <v>900</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J71" s="2">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="K71" s="2">
-        <v>900</v>
+        <v>680</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>67</v>
@@ -7900,48 +7881,51 @@
         <v>56</v>
       </c>
       <c r="AF71" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AG71" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI71" s="2">
+        <v>40024</v>
       </c>
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>252152</v>
+        <v>252140</v>
       </c>
       <c r="B72" s="3">
-        <v>45842</v>
+        <v>45845</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D72" s="3">
-        <v>45828</v>
+        <v>45845</v>
       </c>
       <c r="E72" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F72" s="2">
-        <v>3284</v>
+        <v>15689</v>
       </c>
       <c r="G72" s="2">
-        <v>216</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>36</v>
+        <v>1236</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J72" s="2">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="K72" s="2">
-        <v>1005</v>
+        <v>858</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="N72" s="4" t="s">
         <v>39</v>
@@ -7950,7 +7934,7 @@
         <v>40</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Q72" s="4" t="s">
         <v>42</v>
@@ -7959,7 +7943,7 @@
         <v>43</v>
       </c>
       <c r="S72" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="T72" s="4" t="s">
         <v>45</v>
@@ -7998,15 +7982,18 @@
         <v>56</v>
       </c>
       <c r="AF72" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG72" s="2">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI72" s="2">
+        <v>40037</v>
       </c>
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>252784</v>
+        <v>252364</v>
       </c>
       <c r="B73" s="3">
         <v>45846</v>
@@ -8015,31 +8002,28 @@
         <v>75</v>
       </c>
       <c r="D73" s="3">
-        <v>45862</v>
+        <v>45835</v>
       </c>
       <c r="E73" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" s="2">
-        <v>3237</v>
+        <v>11346</v>
       </c>
       <c r="G73" s="2">
-        <v>165</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>103</v>
+        <v>500</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J73" s="2">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="K73" s="2">
-        <v>425</v>
+        <v>546</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>67</v>
@@ -8099,51 +8083,44 @@
         <v>56</v>
       </c>
       <c r="AF73" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG73" s="2">
-        <v>95</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AH73" s="10"/>
+      <c r="AI73" s="11"/>
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>252402</v>
+        <v>252418</v>
       </c>
       <c r="B74" s="3">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D74" s="3">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="E74" s="2">
         <v>6</v>
       </c>
       <c r="F74" s="2">
-        <v>3009</v>
+        <v>8985</v>
       </c>
       <c r="G74" s="2">
-        <v>174</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>103</v>
+        <v>285</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J74" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="K74" s="2">
-        <v>1020</v>
+        <v>600</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="N74" s="4" t="s">
         <v>39</v>
@@ -8152,37 +8129,37 @@
         <v>40</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="Q74" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R74" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S74" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="T74" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U74" s="4" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="V74" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="W74" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X74" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="Y74" s="4" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="Z74" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="AA74" s="4" t="s">
         <v>52</v>
@@ -8200,84 +8177,81 @@
         <v>56</v>
       </c>
       <c r="AF74" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG74" s="2">
-        <v>20</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AH74" s="10"/>
+      <c r="AI74" s="11"/>
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>252978</v>
-      </c>
-      <c r="B75" s="3">
+      <c r="A75" s="8">
+        <v>252476</v>
+      </c>
+      <c r="B75" s="9">
+        <v>45846</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" s="9">
         <v>45845</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="3">
-        <v>45824</v>
-      </c>
-      <c r="E75" s="2">
-        <v>1</v>
-      </c>
-      <c r="F75" s="2">
-        <v>2796</v>
-      </c>
-      <c r="G75" s="2">
-        <v>245</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I75" s="4" t="s">
+      <c r="E75" s="8">
+        <v>3</v>
+      </c>
+      <c r="F75" s="8">
+        <v>8681</v>
+      </c>
+      <c r="G75" s="8">
+        <v>500</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J75" s="2">
-        <v>580</v>
-      </c>
-      <c r="K75" s="2">
-        <v>1160</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M75" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="N75" s="4" t="s">
+      <c r="J75" s="8">
+        <v>345</v>
+      </c>
+      <c r="K75" s="8">
+        <v>690</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N75" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="O75" s="4" t="s">
+      <c r="O75" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="P75" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q75" s="4" t="s">
+      <c r="P75" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q75" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="R75" s="4" t="s">
+      <c r="R75" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S75" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="T75" s="4" t="s">
+      <c r="S75" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T75" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="U75" s="4" t="s">
+      <c r="U75" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="V75" s="4" t="s">
+      <c r="V75" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="W75" s="4" t="s">
+      <c r="W75" s="10" t="s">
         <v>48</v>
       </c>
       <c r="X75" s="4" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="Y75" s="4" t="s">
         <v>50</v>
@@ -8301,45 +8275,47 @@
         <v>56</v>
       </c>
       <c r="AF75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG75" s="2">
-        <v>12</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AH75" s="10"/>
+      <c r="AI75" s="11"/>
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>243569</v>
+        <v>252047</v>
       </c>
       <c r="B76" s="3">
-        <v>45561</v>
+        <v>45841</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D76" s="3">
-        <v>45551</v>
+        <v>45837</v>
       </c>
       <c r="E76" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F76" s="2">
-        <v>2601</v>
+        <v>8506</v>
       </c>
       <c r="G76" s="2">
-        <v>364</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>63</v>
+        <v>601</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J76" s="2">
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="K76" s="2">
-        <v>1140</v>
+        <v>940</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>64</v>
@@ -8360,7 +8336,7 @@
         <v>43</v>
       </c>
       <c r="S76" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="T76" s="4" t="s">
         <v>45</v>
@@ -8375,7 +8351,7 @@
         <v>48</v>
       </c>
       <c r="X76" s="4" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="Y76" s="4" t="s">
         <v>50</v>
@@ -8401,40 +8377,45 @@
       <c r="AF76" s="2">
         <v>1</v>
       </c>
-      <c r="AG76" s="2">
-        <v>16</v>
-      </c>
+      <c r="AH76" s="10"/>
+      <c r="AI76" s="11"/>
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>252980</v>
+        <v>252146</v>
       </c>
       <c r="B77" s="3">
-        <v>45844</v>
+        <v>45841</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D77" s="3">
-        <v>45908</v>
+        <v>45837</v>
       </c>
       <c r="E77" s="2">
         <v>6</v>
       </c>
       <c r="F77" s="2">
-        <v>2049</v>
+        <v>7996</v>
       </c>
       <c r="G77" s="2">
-        <v>100</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>103</v>
+        <v>565</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>77</v>
+        <v>37</v>
+      </c>
+      <c r="J77" s="2">
+        <v>470</v>
       </c>
       <c r="K77" s="2">
-        <v>700</v>
+        <v>940</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>39</v>
@@ -8443,37 +8424,37 @@
         <v>40</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="Q77" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R77" s="4" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="S77" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="T77" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U77" s="4" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="V77" s="4" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="W77" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X77" s="4" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="Y77" s="4" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Z77" s="4" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="AA77" s="4" t="s">
         <v>52</v>
@@ -8491,92 +8472,147 @@
         <v>56</v>
       </c>
       <c r="AF77" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH77" s="10"/>
+      <c r="AI77" s="11"/>
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>252983</v>
+        <v>252470</v>
       </c>
       <c r="B78" s="3">
-        <v>45847</v>
+        <v>45849</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D78" s="3">
-        <v>45862</v>
+        <v>45842</v>
       </c>
       <c r="E78" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F78" s="2">
-        <v>1912</v>
+        <v>7500</v>
       </c>
       <c r="G78" s="2">
-        <v>97</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J78" s="2">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="K78" s="2">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>101</v>
       </c>
+      <c r="M78" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="N78" s="4" t="s">
-        <v>74</v>
+        <v>39</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q78" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R78" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S78" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T78" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U78" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V78" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W78" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X78" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y78" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z78" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA78" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB78" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC78" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD78" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE78" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="AF78" s="2">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG78" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH78" s="10"/>
+      <c r="AI78" s="11"/>
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>252790</v>
+        <v>252144</v>
       </c>
       <c r="B79" s="3">
-        <v>45848</v>
+        <v>45841</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D79" s="3">
-        <v>45863</v>
+        <v>45837</v>
       </c>
       <c r="E79" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F79" s="2">
-        <v>1453</v>
+        <v>6496</v>
       </c>
       <c r="G79" s="2">
-        <v>106</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>116</v>
+        <v>459</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J79" s="2">
-        <v>200</v>
+        <v>470</v>
       </c>
       <c r="K79" s="2">
-        <v>800</v>
+        <v>940</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N79" s="4" t="s">
         <v>39</v>
@@ -8585,7 +8621,7 @@
         <v>40</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="Q79" s="4" t="s">
         <v>42</v>
@@ -8594,7 +8630,7 @@
         <v>43</v>
       </c>
       <c r="S79" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T79" s="4" t="s">
         <v>45</v>
@@ -8633,48 +8669,44 @@
         <v>56</v>
       </c>
       <c r="AF79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="2">
-        <v>12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH79" s="10"/>
+      <c r="AI79" s="11"/>
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>252783</v>
+        <v>252665</v>
       </c>
       <c r="B80" s="3">
-        <v>45846</v>
+        <v>45844</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D80" s="3">
-        <v>45862</v>
+        <v>45902</v>
       </c>
       <c r="E80" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F80" s="2">
-        <v>1434</v>
+        <v>5865</v>
       </c>
       <c r="G80" s="2">
-        <v>73</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J80" s="2">
-        <v>85</v>
+        <v>775</v>
       </c>
       <c r="K80" s="2">
-        <v>425</v>
+        <v>775</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>67</v>
@@ -8710,7 +8742,7 @@
         <v>48</v>
       </c>
       <c r="X80" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y80" s="4" t="s">
         <v>50</v>
@@ -8734,51 +8766,44 @@
         <v>56</v>
       </c>
       <c r="AF80" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG80" s="2">
-        <v>45</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AH80" s="10"/>
+      <c r="AI80" s="11"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>252636</v>
+        <v>252417</v>
       </c>
       <c r="B81" s="3">
-        <v>45842</v>
+        <v>45840</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D81" s="3">
-        <v>45848</v>
+        <v>45838</v>
       </c>
       <c r="E81" s="2">
         <v>6</v>
       </c>
       <c r="F81" s="2">
-        <v>1353</v>
+        <v>4711</v>
       </c>
       <c r="G81" s="2">
-        <v>71</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J81" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="K81" s="2">
-        <v>780</v>
+        <v>720</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="M81" s="4" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="N81" s="4" t="s">
         <v>39</v>
@@ -8787,37 +8812,37 @@
         <v>40</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="Q81" s="4" t="s">
         <v>42</v>
       </c>
       <c r="R81" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S81" s="4" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="T81" s="4" t="s">
         <v>45</v>
       </c>
       <c r="U81" s="4" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="V81" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="W81" s="4" t="s">
         <v>48</v>
       </c>
       <c r="X81" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="Y81" s="4" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="Z81" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="AA81" s="4" t="s">
         <v>52</v>
@@ -8837,46 +8862,42 @@
       <c r="AF81" s="2">
         <v>0</v>
       </c>
-      <c r="AG81" s="2">
-        <v>20</v>
-      </c>
+      <c r="AH81" s="10"/>
+      <c r="AI81" s="11"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>244023</v>
+        <v>251849</v>
       </c>
       <c r="B82" s="3">
-        <v>45552</v>
+        <v>45846</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D82" s="3">
-        <v>45565</v>
+        <v>45833</v>
       </c>
       <c r="E82" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" s="2">
-        <v>997</v>
+        <v>4006</v>
       </c>
       <c r="G82" s="2">
-        <v>59</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J82" s="2">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="K82" s="2">
-        <v>860</v>
+        <v>768</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>67</v>
@@ -8938,14 +8959,17 @@
       <c r="AF82" s="2">
         <v>0</v>
       </c>
-      <c r="AG82" s="2">
-        <v>5</v>
+      <c r="AH82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI82" s="2">
+        <v>40042</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AI82" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI82">
-      <sortCondition descending="1" ref="F1:F82"/>
+      <sortCondition descending="1" ref="H1:H82"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
